--- a/samples/demo/供应商A报价表_v2.xlsx
+++ b/samples/demo/供应商A报价表_v2.xlsx
@@ -1014,7 +1014,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Volvo VN 2004-2017</t>
+          <t>Volvo VN 2006-2017</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
